--- a/enhancements/test-files/06_PC_pc0303_2026_cases.xlsx
+++ b/enhancements/test-files/06_PC_pc0303_2026_cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -432,6 +432,13 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,6 +487,41 @@
           <t>Transaction Effective Date</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MarketProvider</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction Detail</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>GrossCommissionAmount</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>CommissionPct</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionAmount</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionPct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -492,12 +534,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Pinnacle Agency Partners</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -506,16 +548,41 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>18312.62</v>
+        <v>24567.17</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>45839</v>
+        <v>45971</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46021</v>
+        <v>46019</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>2948.06</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1385.59</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0564</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1562.47</v>
       </c>
     </row>
     <row r="3">
@@ -526,12 +593,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Liberty Mutual</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Apex Insurance Brokers</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -540,16 +607,41 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>12419.55</v>
+        <v>17110.8</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>46026</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>46005</v>
+        <v>45958</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46024</v>
+        <v>46026</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>2053.3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N3" t="n">
+        <v>882.92</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0516</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1170.38</v>
       </c>
     </row>
     <row r="4">
@@ -563,12 +655,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Metro Agency Group</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -577,27 +669,52 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>18811.58</v>
+        <v>11619.34</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>45873</v>
+        <v>45983</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46053</v>
+        <v>46049</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1394.32</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N4" t="n">
+        <v>641.39</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0552</v>
+      </c>
+      <c r="P4" t="n">
+        <v>752.9299999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>Zenith Insurance Group</t>
+          <t>Liberty Mutual</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Metro Agency Group</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -606,16 +723,41 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>12782.25</v>
+        <v>13636.75</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46057</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>45757</v>
+        <v>45906</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46056</v>
+        <v>46054</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1636.41</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N5" t="n">
+        <v>818.21</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P5" t="n">
+        <v>818.21</v>
       </c>
     </row>
     <row r="6">
@@ -629,12 +771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Liberty Mutual</t>
+          <t>National Indemnity Co</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Coastal Risk Advisors</t>
+          <t>Metro Agency Group</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -643,16 +785,41 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>20330.2</v>
+        <v>7183.23</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>46051</v>
+        <v>45853</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>46079</v>
+        <v>46080</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>861.99</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N6" t="n">
+        <v>387.9</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="P6" t="n">
+        <v>474.09</v>
       </c>
     </row>
     <row r="7">
@@ -666,12 +833,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Liberty Mutual</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Apex Insurance Brokers</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -680,16 +847,41 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>15547.39</v>
+        <v>21596.54</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46085</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>45852</v>
+        <v>45917</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>46082</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>2591.58</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1192.13</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0552</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1399.45</v>
       </c>
     </row>
   </sheetData>
